--- a/data/trans_dic/IP13_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas</t>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,22</t>
+          <t>1,08; 9,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,32</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,92</t>
+          <t>1,4; 6,6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,36</t>
+          <t>1,22; 7,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,78</t>
+          <t>1,0; 5,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,25</t>
+          <t>1,53; 5,52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 11,48</t>
+          <t>1,11; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,57</t>
+          <t>1,02; 10,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,19</t>
+          <t>1,85; 8,33</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 9,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,92</t>
+          <t>0,41; 5,94</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 15,76</t>
+          <t>2,65; 16,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 15,29</t>
+          <t>1,55; 15,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,45</t>
+          <t>3,13; 12,09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,46</t>
+          <t>1,13; 10,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 14,15</t>
+          <t>2,01; 12,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,96</t>
+          <t>2,36; 9,55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 9,32</t>
+          <t>2,52; 9,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,37</t>
+          <t>5,11; 13,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,04</t>
+          <t>4,62; 10,32</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,21</t>
+          <t>1,42; 6,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,74</t>
+          <t>2,67; 9,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,46</t>
+          <t>2,64; 6,66</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,46</t>
+          <t>2,86; 5,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,2</t>
+          <t>3,45; 6,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,51</t>
+          <t>3,61; 5,43</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3420</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>792; 7253</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6012</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2141; 10075</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7729</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1544; 9744</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1280; 7504</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3892; 14040</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5441</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>648; 6843</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>684; 7155</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2315; 10452</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 7366</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>606; 8805</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2526</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>915; 5817</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>632; 6301</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2352; 9099</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1761</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5029</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>523; 5040</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1131; 6927</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2414; 9775</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>6331</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13536</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>19867</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3140; 11606</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7938; 20529</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12935; 28869</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4258</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8039</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>12297</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1866; 8132</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>4181; 14363</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>7614; 19216</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>63411</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>19011; 36467</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>26271; 47471</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>51509; 77482</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,9</t>
+          <t>1,72; 10,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 7,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,6</t>
+          <t>1,26; 6,85</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,68</t>
+          <t>1,25; 8,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,88</t>
+          <t>1,01; 5,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,52</t>
+          <t>1,5; 5,3</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 11,74</t>
+          <t>1,59; 12,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,65</t>
+          <t>1,06; 11,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,33</t>
+          <t>1,84; 9,44</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,43</t>
+          <t>0,0; 7,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,94</t>
+          <t>0,42; 5,7</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 16,85</t>
+          <t>2,88; 16,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 15,47</t>
+          <t>1,43; 14,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 12,09</t>
+          <t>2,99; 12,87</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,92</t>
+          <t>1,16; 10,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,33</t>
+          <t>1,96; 12,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,55</t>
+          <t>2,19; 9,63</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,32</t>
+          <t>2,36; 9,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,22</t>
+          <t>5,15; 13,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,32</t>
+          <t>4,78; 9,94</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,18</t>
+          <t>1,45; 6,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,16</t>
+          <t>2,67; 9,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,66</t>
+          <t>2,64; 6,64</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,48</t>
+          <t>2,84; 5,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,24</t>
+          <t>3,61; 6,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,43</t>
+          <t>3,59; 5,46</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>792; 7253</t>
+          <t>1263; 7767</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6012</t>
+          <t>0; 5878</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2141; 10075</t>
+          <t>1924; 10462</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1544; 9744</t>
+          <t>1583; 10259</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1280; 7504</t>
+          <t>1288; 7626</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3892; 14040</t>
+          <t>3805; 13483</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>648; 6843</t>
+          <t>926; 7141</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>684; 7155</t>
+          <t>712; 7675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2315; 10452</t>
+          <t>2313; 11834</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5226</t>
+          <t>0; 5027</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7366</t>
+          <t>0; 5903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>606; 8805</t>
+          <t>629; 8453</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>915; 5817</t>
+          <t>994; 5565</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>632; 6301</t>
+          <t>581; 5846</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2352; 9099</t>
+          <t>2246; 9684</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>523; 5040</t>
+          <t>536; 4887</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1131; 6927</t>
+          <t>1100; 7100</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2414; 9775</t>
+          <t>2246; 9860</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3140; 11606</t>
+          <t>2939; 11771</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7938; 20529</t>
+          <t>8000; 21319</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12935; 28869</t>
+          <t>13374; 27822</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1866; 8132</t>
+          <t>1911; 8295</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4181; 14363</t>
+          <t>4187; 14162</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7614; 19216</t>
+          <t>7617; 19149</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>19011; 36467</t>
+          <t>18874; 35042</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26271; 47471</t>
+          <t>27485; 48516</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51509; 77482</t>
+          <t>51166; 77859</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,6</t>
+          <t>0,0; 8,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>2,0; 11,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,85</t>
+          <t>1,55; 7,65</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,09</t>
+          <t>0,85; 5,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,98</t>
+          <t>1,57; 8,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,3</t>
+          <t>1,81; 6,07</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 12,26</t>
+          <t>0,94; 9,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 11,43</t>
+          <t>1,14; 10,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,44</t>
+          <t>1,89; 7,73</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,55</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,7</t>
+          <t>0,38; 6,36</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 16,12</t>
+          <t>1,62; 15,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 14,36</t>
+          <t>2,27; 16,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,87</t>
+          <t>3,38; 13,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,59</t>
+          <t>2,26; 13,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 12,64</t>
+          <t>1,22; 10,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,63</t>
+          <t>2,2; 8,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,45</t>
+          <t>5,5; 14,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,73</t>
+          <t>2,62; 9,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,94</t>
+          <t>4,83; 10,37</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,3</t>
+          <t>2,5; 8,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,03</t>
+          <t>1,13; 5,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,64</t>
+          <t>2,26; 6,14</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,27</t>
+          <t>3,71; 6,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,37</t>
+          <t>3,01; 5,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,46</t>
+          <t>3,72; 5,6</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>4597</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1263; 7767</t>
+          <t>0; 5679</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5878</t>
+          <t>1127; 6591</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1924; 10462</t>
+          <t>1871; 9230</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7358</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1583; 10259</t>
+          <t>986; 6462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1288; 7626</t>
+          <t>1579; 8984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3805; 13483</t>
+          <t>3918; 13125</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>4811</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>926; 7141</t>
+          <t>557; 5802</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>712; 7675</t>
+          <t>644; 5851</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2313; 11834</t>
+          <t>2191; 8965</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2825</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5027</t>
+          <t>0; 5796</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5903</t>
+          <t>0; 7207</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>629; 8453</t>
+          <t>542; 9098</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5205</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>994; 5565</t>
+          <t>640; 6259</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>581; 5846</t>
+          <t>808; 5715</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2246; 9684</t>
+          <t>2542; 9772</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4535</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>536; 4887</t>
+          <t>1108; 6684</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1100; 7100</t>
+          <t>558; 4615</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2246; 9860</t>
+          <t>2081; 8281</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19352</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2939; 11771</t>
+          <t>7746; 19739</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8000; 21319</t>
+          <t>3216; 11935</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13374; 27822</t>
+          <t>12715; 27323</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>11791</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1911; 8295</t>
+          <t>3992; 13937</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4187; 14162</t>
+          <t>1581; 7208</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7617; 19149</t>
+          <t>6772; 18403</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18874; 35042</t>
+          <t>26014; 44933</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>27485; 48516</t>
+          <t>18945; 35016</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51166; 77859</t>
+          <t>49431; 74402</t>
         </is>
       </c>
     </row>
